--- a/output/03_Aviat_발주이벤트_분석.xlsx
+++ b/output/03_Aviat_발주이벤트_분석.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'이벤트별_BoM'!$A$1:$M$246</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'후속발주_후보'!$A$1:$K$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'대량일괄발주'!$A$1:$G$237</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'단품·예비품'!$A$1:$I$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'단품·예비품'!$A$1:$I$238</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'판정근거'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -677,7 +677,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Antenna, CPU/Control, Cable, Coupler/Hybrid, Duplexer, Fan, Interface Card, License, Modem, Mount/Bracket, OBC2, ODU/RFU, PDP/Power, SFP/Optical Module, Surge/Grounding, Waveguide, 기타</t>
+          <t>Antenna, CPU/Control, Cable, Coupler/Hybrid, Duplexer, Fan, IDU/Chassis, Interface Card, License, Modem, Mount/Bracket, OBC2, ODU/RFU, PDP/Power, SFP/Optical Module, Surge/Grounding, Waveguide, 기타</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Antenna, Cable, Coupler/Hybrid, Fan, Interface Card, License, Modem, Mount/Bracket, ODU/RFU, SFP/Optical Module, Surge/Grounding, Waveguide</t>
+          <t>Antenna, Cable, Coupler/Hybrid, Fan, IDU/Chassis, Interface Card, License, Modem, Mount/Bracket, ODU/RFU, SFP/Optical Module, Surge/Grounding, Waveguide</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>CPU/Control, Cable, Connector, Coupler/Hybrid, Duplexer, Fan, Interface Card, License, Modem, Mount/Bracket, OBC2, ODU/RFU, PDP/Power, SFP/Optical Module, Surge/Grounding, WBX, WTM, Waveguide, 기타</t>
+          <t>CPU/Control, Cable, Connector, Coupler/Hybrid, Duplexer, Fan, IDU/Chassis, Interface Card, License, Modem, Mount/Bracket, OBC2, ODU/RFU, PDP/Power, SFP/Optical Module, Surge/Grounding, WBX, WTM, Waveguide, 기타</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Cable, Connector, Coupler/Hybrid, Fan, Interface Card, License, Modem, Mount/Bracket, ODU/RFU, PDP/Power, SFP/Optical Module, Surge/Grounding, WBX, WTM, Waveguide, 기타</t>
+          <t>Cable, Connector, Coupler/Hybrid, Fan, IDU/Chassis, License, Modem, Mount/Bracket, ODU/RFU, PDP/Power, SFP/Optical Module, Surge/Grounding, WBX, WTM, Waveguide, 기타</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Cable, Coupler/Hybrid, Fan, Interface Card, License, Modem, Mount/Bracket, ODU/RFU, SFP/Optical Module, Surge/Grounding, Waveguide</t>
+          <t>Cable, Coupler/Hybrid, Fan, IDU/Chassis, License, Modem, Mount/Bracket, ODU/RFU, SFP/Optical Module, Surge/Grounding, Waveguide</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Antenna, CPU/Control, Coupler/Hybrid, Fan, Interface Card, License, Modem, Mount/Bracket, ODU/RFU, PDP/Power, SFP/Optical Module</t>
+          <t>Antenna, CPU/Control, Coupler/Hybrid, Fan, IDU/Chassis, Interface Card, License, Modem, Mount/Bracket, ODU/RFU, PDP/Power, SFP/Optical Module</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
@@ -1636,27 +1636,27 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>유력</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>낮음</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>신규 Chassis 없이 ODU/License/Interface Card 등 일부 구성군만 나타남 → 기존 설치에 대한 증설·교체 가능성. (포함 품목군: Interface Card)</t>
+          <t>서로 다른 품목 1종만 존재 → 단품 또는 예비품 보충으로 추정.</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Antenna, CPU/Control, Cable, Connector, Fan, Interface Card, License, Modem, Mount/Bracket, ODU/RFU, PDP/Power, SFP/Optical Module, Surge/Grounding, WBX, WTM, Waveguide, 기타</t>
+          <t>Antenna, CPU/Control, Cable, Connector, Fan, IDU/Chassis, Interface Card, License, Modem, Mount/Bracket, ODU/RFU, PDP/Power, SFP/Optical Module, Surge/Grounding, WBX, WTM, Waveguide, 기타</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Cable, Coupler/Hybrid, Fan, Interface Card, License, Modem, Mount/Bracket, ODU/RFU, SFP/Optical Module, Surge/Grounding, Waveguide</t>
+          <t>Cable, Coupler/Hybrid, Fan, IDU/Chassis, License, Modem, Mount/Bracket, ODU/RFU, SFP/Optical Module, Surge/Grounding, Waveguide</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="F13" s="2" t="n"/>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F40" s="2" t="n"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="F56" s="2" t="n"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F65" s="2" t="n"/>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F106" s="2" t="n"/>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F116" s="2" t="n"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="F136" s="2" t="n"/>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F142" s="2" t="n"/>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F149" s="2" t="n"/>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F163" s="2" t="n"/>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F188" s="2" t="n"/>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F190" s="2" t="n"/>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F191" s="2" t="n"/>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F217" s="2" t="n"/>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F219" s="2" t="n"/>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F241" s="2" t="n"/>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Antenna, CPU/Control, Cable, Coupler/Hybrid, Duplexer, Fan, Interface Card, License, Modem, Mount/Bracket, OBC2, ODU/RFU, PDP/Power, SFP/Optical Module, Surge/Grounding, Waveguide, 기타</t>
+          <t>Antenna, CPU/Control, Cable, Coupler/Hybrid, Duplexer, Fan, IDU/Chassis, Interface Card, License, Modem, Mount/Bracket, OBC2, ODU/RFU, PDP/Power, SFP/Optical Module, Surge/Grounding, Waveguide, 기타</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Antenna, Cable, Coupler/Hybrid, Fan, Interface Card, Modem, ODU/RFU, SFP/Optical Module, Surge/Grounding</t>
+          <t>Antenna, Cable, Coupler/Hybrid, Fan, IDU/Chassis, Interface Card, Modem, ODU/RFU, SFP/Optical Module, Surge/Grounding</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>IDU/Chassis, PDP/Power</t>
+          <t>PDP/Power</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I237"/>
+  <dimension ref="A1:I238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21593,7 +21593,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -22754,7 +22754,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -23313,7 +23313,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -23700,7 +23700,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
@@ -26753,7 +26753,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="H133" s="2" t="n">
@@ -27011,7 +27011,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H139" s="2" t="n">
@@ -27312,7 +27312,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H146" s="2" t="n">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H160" s="2" t="n">
@@ -28774,7 +28774,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H180" s="2" t="n">
@@ -28860,7 +28860,7 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H182" s="2" t="n">
@@ -28875,43 +28875,43 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>EVT-012</t>
+          <t>EVT-011</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>46135</v>
+        <v>46018</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>이상헌</t>
+          <t>이상*</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>강남유선시설2팀</t>
+          <t>그룹시설팀</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>K9210625</t>
+          <t>K9208698</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>N-TYPE MALE TO PDR48 ADAPTER 4GHz</t>
+          <t>VR4 1RU CHASSIS</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H183" s="2" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>가능성 있음</t>
+          <t>유력</t>
         </is>
       </c>
     </row>
@@ -28936,21 +28936,21 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>K9210624</t>
+          <t>K9210625</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE</t>
+          <t>N-TYPE MALE TO PDR48 ADAPTER 4GHz</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Waveguide</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="H184" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
@@ -28979,12 +28979,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>K9210623</t>
+          <t>K9210624</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
+          <t>FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -28993,7 +28993,7 @@
         </is>
       </c>
       <c r="H185" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
@@ -29022,21 +29022,21 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>K9210622</t>
+          <t>K9210623</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>6GHz IAP3 Mounting Bracket</t>
+          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Mount/Bracket</t>
+          <t>Waveguide</t>
         </is>
       </c>
       <c r="H186" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
@@ -29065,21 +29065,21 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>K9210616</t>
+          <t>K9210622</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>HAX_L6GHz ODU IAP3 HIGH</t>
+          <t>6GHz IAP3 Mounting Bracket</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>Mount/Bracket</t>
         </is>
       </c>
       <c r="H187" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
@@ -29108,12 +29108,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>K9210615</t>
+          <t>K9210616</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>HAX_L6GHz ODU IAP3 LOW</t>
+          <t>HAX_L6GHz ODU IAP3 HIGH</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -29122,7 +29122,7 @@
         </is>
       </c>
       <c r="H188" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
@@ -29151,17 +29151,17 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>K9210611</t>
+          <t>K9210615</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>HAX_4GHz WBX 4 CHANNEL</t>
+          <t>HAX_L6GHz ODU IAP3 LOW</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>WBX</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="H189" s="2" t="n">
@@ -29194,21 +29194,21 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>K9210610</t>
+          <t>K9210611</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>HAX_WTM 4500XT 4GHz</t>
+          <t>HAX_4GHz WBX 4 CHANNEL</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>WTM</t>
+          <t>WBX</t>
         </is>
       </c>
       <c r="H190" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
@@ -29237,21 +29237,21 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>K9208734</t>
+          <t>K9210610</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>VR10 Node License</t>
+          <t>HAX_WTM 4500XT 4GHz</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>WTM</t>
         </is>
       </c>
       <c r="H191" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
@@ -29280,12 +29280,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>K9208733</t>
+          <t>K9208734</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>VR4 Node License</t>
+          <t>VR10 Node License</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -29294,7 +29294,7 @@
         </is>
       </c>
       <c r="H192" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
@@ -29323,21 +29323,21 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>K9208731</t>
+          <t>K9208733</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10</t>
+          <t>VR4 Node License</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Modem</t>
+          <t>License</t>
         </is>
       </c>
       <c r="H193" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
@@ -29366,21 +29366,21 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>K9208729</t>
+          <t>K9208731</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>10/11GHz IAP3 Mounting Bracket</t>
+          <t>MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Mount/Bracket</t>
+          <t>Modem</t>
         </is>
       </c>
       <c r="H194" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
@@ -29409,12 +29409,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>K9208728</t>
+          <t>K9208729</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>7/8GHz IAP3 Mounting Bracket</t>
+          <t>10/11GHz IAP3 Mounting Bracket</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -29423,7 +29423,7 @@
         </is>
       </c>
       <c r="H195" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
@@ -29452,17 +29452,17 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>K9208717</t>
+          <t>K9208728</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>11GHz ODU IAP3 HIGH</t>
+          <t>7/8GHz IAP3 Mounting Bracket</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>Mount/Bracket</t>
         </is>
       </c>
       <c r="H196" s="2" t="n">
@@ -29495,12 +29495,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>K9208716</t>
+          <t>K9208717</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>11GHz ODU IAP3 LOW</t>
+          <t>11GHz ODU IAP3 HIGH</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -29509,7 +29509,7 @@
         </is>
       </c>
       <c r="H197" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
@@ -29538,12 +29538,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>K9208715</t>
+          <t>K9208716</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>8GHz ODU IAP3 HIGH</t>
+          <t>11GHz ODU IAP3 LOW</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -29552,7 +29552,7 @@
         </is>
       </c>
       <c r="H198" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
@@ -29581,12 +29581,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>K9208714</t>
+          <t>K9208715</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>8GHz ODU IAP3 LOW</t>
+          <t>8GHz ODU IAP3 HIGH</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -29595,7 +29595,7 @@
         </is>
       </c>
       <c r="H199" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
@@ -29624,21 +29624,21 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>K9208711</t>
+          <t>K9208714</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>MC-MV Redundancy</t>
+          <t>8GHz ODU IAP3 LOW</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>CPU/Control</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="H200" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
@@ -29667,21 +29667,21 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>K9208707</t>
+          <t>K9208711</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>GbE4e-AV</t>
+          <t>MC-MV Redundancy</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>CPU/Control</t>
         </is>
       </c>
       <c r="H201" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
@@ -29710,12 +29710,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>K9208706</t>
+          <t>K9208707</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>GbE4f-AV</t>
+          <t>GbE4e-AV</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="H202" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
@@ -29753,21 +29753,21 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>K9208705</t>
+          <t>K9208706</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>MODEM-AV</t>
+          <t>GbE4f-AV</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Modem</t>
+          <t>Interface Card</t>
         </is>
       </c>
       <c r="H203" s="2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
@@ -29796,21 +29796,21 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>K9208704</t>
+          <t>K9208705</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>PS-MV</t>
+          <t>MODEM-AV</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>PDP/Power</t>
+          <t>Modem</t>
         </is>
       </c>
       <c r="H204" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
@@ -29839,21 +29839,21 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>K9208703</t>
+          <t>K9208704</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>TERM-MV</t>
+          <t>PS-MV</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>CPU/Control</t>
+          <t>PDP/Power</t>
         </is>
       </c>
       <c r="H205" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
@@ -29882,21 +29882,21 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>K9208702</t>
+          <t>K9208703</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>FAN-MV</t>
+          <t>TERM-MV</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Fan</t>
+          <t>CPU/Control</t>
         </is>
       </c>
       <c r="H206" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
@@ -29925,21 +29925,21 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>K9208701</t>
+          <t>K9208702</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>VR10 MC-MV</t>
+          <t>FAN-MV</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>CPU/Control</t>
+          <t>Fan</t>
         </is>
       </c>
       <c r="H207" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
@@ -29968,17 +29968,17 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>K9208700</t>
+          <t>K9208701</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>VR10 3RU CHASSIS</t>
+          <t>VR10 MC-MV</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>CPU/Control</t>
         </is>
       </c>
       <c r="H208" s="2" t="n">
@@ -30011,17 +30011,17 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>K9208699</t>
+          <t>K9208700</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>FAN-CV</t>
+          <t>VR10 3RU CHASSIS</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Fan</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H209" s="2" t="n">
@@ -30054,17 +30054,17 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>K9208698</t>
+          <t>K9208699</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>VR4 1RU CHASSIS</t>
+          <t>FAN-CV</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Fan</t>
         </is>
       </c>
       <c r="H210" s="2" t="n">
@@ -30097,21 +30097,21 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>K9204033</t>
+          <t>K9208698</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>HAX_WTM4500 NODE LICENSE</t>
+          <t>VR4 1RU CHASSIS</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H211" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
@@ -30140,17 +30140,17 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>K9204032</t>
+          <t>K9204033</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>HAX_GROUND CONDUCTOR</t>
+          <t>HAX_WTM4500 NODE LICENSE</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Surge/Grounding</t>
+          <t>License</t>
         </is>
       </c>
       <c r="H212" s="2" t="n">
@@ -30183,12 +30183,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>K9204030</t>
+          <t>K9204032</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>HAX_PROTECTOR MODULE</t>
+          <t>HAX_GROUND CONDUCTOR</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -30197,7 +30197,7 @@
         </is>
       </c>
       <c r="H213" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
@@ -30226,21 +30226,21 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>K9204029</t>
+          <t>K9204030</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>HAX_MULTI-ETHERNET CABLE 100M</t>
+          <t>HAX_PROTECTOR MODULE</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Surge/Grounding</t>
         </is>
       </c>
       <c r="H214" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>K9204028</t>
+          <t>K9204029</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>HAX_MULTI-FIBER CABLE 100M</t>
+          <t>HAX_MULTI-ETHERNET CABLE 100M</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -30312,12 +30312,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>K9204027</t>
+          <t>K9204028</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>HAX_MULTI POWER CABLE 100M</t>
+          <t>HAX_MULTI-FIBER CABLE 100M</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -30355,21 +30355,21 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>K9204026</t>
+          <t>K9204027</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>HAX_WEATHERPROOFING KIT</t>
+          <t>HAX_MULTI POWER CABLE 100M</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="H217" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
@@ -30398,21 +30398,21 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>K9198328</t>
+          <t>K9204026</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>Gigabit Ethernet SFP_Industrial_-40~+85℃_실외형</t>
+          <t>HAX_WEATHERPROOFING KIT</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="H218" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
@@ -30441,21 +30441,21 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>K9193435</t>
+          <t>K9198328</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>ANT-HP-DP-4FT-8</t>
+          <t>Gigabit Ethernet SFP_Industrial_-40~+85℃_실외형</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Antenna</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
@@ -30484,21 +30484,21 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>K9210278</t>
+          <t>K9193435</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>M/W장치</t>
+          <t>ANT-HP-DP-4FT-8</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>Antenna</t>
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
@@ -30527,21 +30527,21 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>K9210279</t>
+          <t>K9210278</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>HAX_Gigabit Ethernet SFP</t>
+          <t>M/W장치</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>SFP/Optical Module</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="H221" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
@@ -30570,21 +30570,21 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>K9210280</t>
+          <t>K9210279</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함)</t>
+          <t>HAX_Gigabit Ethernet SFP</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Surge/Grounding</t>
+          <t>SFP/Optical Module</t>
         </is>
       </c>
       <c r="H222" s="2" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
@@ -30613,21 +30613,21 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>K9210281</t>
+          <t>K9210280</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>HAX_커넥터 KIT_IF 케이블 종단용</t>
+          <t>HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함)</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Surge/Grounding</t>
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
@@ -30656,21 +30656,21 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>K9090174</t>
+          <t>K9210281</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>HAX_IDU/ODU간 IF 케이블,1Meter</t>
+          <t>HAX_커넥터 KIT_IF 케이블 종단용</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="H224" s="2" t="n">
-        <v>1200</v>
+        <v>64</v>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
@@ -30681,39 +30681,39 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>EVT-013</t>
+          <t>EVT-012</t>
         </is>
       </c>
       <c r="B225" s="3" t="n">
-        <v>46139</v>
+        <v>46135</v>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>이충환</t>
+          <t>이상헌</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>전라유선시설팀</t>
+          <t>강남유선시설2팀</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>K9208733</t>
+          <t>K9090174</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>VR4 Node License</t>
+          <t>HAX_IDU/ODU간 IF 케이블,1Meter</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="H225" s="2" t="n">
-        <v>4</v>
+        <v>1200</v>
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
@@ -30742,21 +30742,21 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>K9208731</t>
+          <t>K9208733</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10</t>
+          <t>VR4 Node License</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Modem</t>
+          <t>License</t>
         </is>
       </c>
       <c r="H226" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
@@ -30785,21 +30785,21 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>K9208728</t>
+          <t>K9208731</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>7/8GHz IAP3 Mounting Bracket</t>
+          <t>MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Mount/Bracket</t>
+          <t>Modem</t>
         </is>
       </c>
       <c r="H227" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
@@ -30828,17 +30828,17 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>K9208726</t>
+          <t>K9208728</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>7/8GHz FLAT HYBRID 7.125, Direct, UMT,3.7dB</t>
+          <t>7/8GHz IAP3 Mounting Bracket</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Coupler/Hybrid</t>
+          <t>Mount/Bracket</t>
         </is>
       </c>
       <c r="H228" s="2" t="n">
@@ -30871,17 +30871,17 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>K9208715</t>
+          <t>K9208726</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>8GHz ODU IAP3 HIGH</t>
+          <t>7/8GHz FLAT HYBRID 7.125, Direct, UMT,3.7dB</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>Coupler/Hybrid</t>
         </is>
       </c>
       <c r="H229" s="2" t="n">
@@ -30914,12 +30914,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>K9208714</t>
+          <t>K9208715</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>8GHz ODU IAP3 LOW</t>
+          <t>8GHz ODU IAP3 HIGH</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -30957,17 +30957,17 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>K9208699</t>
+          <t>K9208714</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>FAN-CV</t>
+          <t>8GHz ODU IAP3 LOW</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Fan</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="H231" s="2" t="n">
@@ -31000,17 +31000,17 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>K9208698</t>
+          <t>K9208699</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>VR4 1RU CHASSIS</t>
+          <t>FAN-CV</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Fan</t>
         </is>
       </c>
       <c r="H232" s="2" t="n">
@@ -31043,17 +31043,17 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>K9178534</t>
+          <t>K9208698</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>M/W장치</t>
+          <t>VR4 1RU CHASSIS</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Waveguide</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="H233" s="2" t="n">
@@ -31086,21 +31086,21 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>K9210279</t>
+          <t>K9178534</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>HAX_Gigabit Ethernet SFP</t>
+          <t>M/W장치</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>SFP/Optical Module</t>
+          <t>Waveguide</t>
         </is>
       </c>
       <c r="H234" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
@@ -31129,21 +31129,21 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>K9210280</t>
+          <t>K9210279</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함)</t>
+          <t>HAX_Gigabit Ethernet SFP</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Surge/Grounding</t>
+          <t>SFP/Optical Module</t>
         </is>
       </c>
       <c r="H235" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
@@ -31172,17 +31172,17 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>K9210281</t>
+          <t>K9210280</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>HAX_커넥터 KIT_IF 케이블 종단용</t>
+          <t>HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함)</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Surge/Grounding</t>
         </is>
       </c>
       <c r="H236" s="2" t="n">
@@ -31215,30 +31215,73 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
+          <t>K9210281</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>HAX_커넥터 KIT_IF 케이블 종단용</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Cable</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>가능성 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>EVT-013</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>46139</v>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>이충환</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>전라유선시설팀</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
           <t>K9090174</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>HAX_IDU/ODU간 IF 케이블,1Meter</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t>ODU/RFU</t>
         </is>
       </c>
-      <c r="H237" s="2" t="n">
+      <c r="H238" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="I237" s="2" t="inlineStr">
+      <c r="I238" s="2" t="inlineStr">
         <is>
           <t>가능성 있음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I237"/>
+  <autoFilter ref="A1:I238"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
